--- a/output/palmer_drought_trendlines/region/Year.xlsx
+++ b/output/palmer_drought_trendlines/region/Year.xlsx
@@ -55,136 +55,136 @@
     <t>West Region</t>
   </si>
   <si>
+    <t>California River Basin</t>
+  </si>
+  <si>
+    <t>Great Basin</t>
+  </si>
+  <si>
+    <t>Rio Grande River Basin</t>
+  </si>
+  <si>
     <t>US Rockies and Westward</t>
   </si>
   <si>
-    <t>Great Basin</t>
-  </si>
-  <si>
     <t>NWS Western Region</t>
   </si>
   <si>
-    <t>California River Basin</t>
-  </si>
-  <si>
-    <t>Rio Grande River Basin</t>
+    <t>Spring Wheat Belt (area weighted)</t>
   </si>
   <si>
     <t>West North Central Region</t>
   </si>
   <si>
-    <t>Spring Wheat Belt (area weighted)</t>
-  </si>
-  <si>
     <t>Cotton Belt (area weighted)</t>
   </si>
   <si>
     <t>Missouri River Basin</t>
   </si>
   <si>
+    <t>Great Plains</t>
+  </si>
+  <si>
     <t>Pacific Northwest Basin</t>
   </si>
   <si>
     <t>Northwest Region</t>
   </si>
   <si>
-    <t>Great Plains</t>
+    <t>Cotton Belt (productivity weighted)</t>
+  </si>
+  <si>
+    <t>Southeast Region</t>
+  </si>
+  <si>
+    <t>South Atlantic-Gulf Basin</t>
   </si>
   <si>
     <t>Contiguous 48 States</t>
   </si>
   <si>
-    <t>Cotton Belt (productivity weighted)</t>
-  </si>
-  <si>
     <t>Primary Hard Red Winter Wheat Belt (area weighted)</t>
   </si>
   <si>
-    <t>Southeast Region</t>
-  </si>
-  <si>
-    <t>South Atlantic-Gulf Basin</t>
+    <t>Souris-Red-Rainy Basin</t>
+  </si>
+  <si>
+    <t>Spring Wheat Belt (productivity weighted)</t>
+  </si>
+  <si>
+    <t>NWS Southern Region</t>
   </si>
   <si>
     <t>Southern Plains and Gulf Coast</t>
   </si>
   <si>
-    <t>NWS Southern Region</t>
-  </si>
-  <si>
-    <t>Souris-Red-Rainy Basin</t>
-  </si>
-  <si>
-    <t>Spring Wheat Belt (productivity weighted)</t>
+    <t>NWS Eastern Region</t>
+  </si>
+  <si>
+    <t>Arkansas-White-Red Basin</t>
+  </si>
+  <si>
+    <t>Mid-Atlantic Basin</t>
   </si>
   <si>
     <t>Winter Wheat Belt (productivity weighted)</t>
   </si>
   <si>
-    <t>Arkansas-White-Red Basin</t>
-  </si>
-  <si>
     <t>Winter Wheat Belt (area weighted)</t>
   </si>
   <si>
-    <t>NWS Eastern Region</t>
-  </si>
-  <si>
     <t>South Region</t>
   </si>
   <si>
-    <t>Mid-Atlantic Basin</t>
+    <t>Northeast Region</t>
   </si>
   <si>
     <t>Texas Gulf Coast River Basin</t>
   </si>
   <si>
-    <t>Northeast Region</t>
-  </si>
-  <si>
     <t>NWS Central Region</t>
   </si>
   <si>
+    <t>Lower Mississippi River Basin</t>
+  </si>
+  <si>
     <t>Mississippi River Basin &amp; Tributaties (N. of Memphis, TN)</t>
   </si>
   <si>
     <t>New England Basin</t>
   </si>
   <si>
-    <t>Lower Mississippi River Basin</t>
+    <t>Tennessee River Basin</t>
+  </si>
+  <si>
+    <t>Soybean Belt (area weighted)</t>
+  </si>
+  <si>
+    <t>Ohio River Basin</t>
+  </si>
+  <si>
+    <t>East North Central Region</t>
+  </si>
+  <si>
+    <t>Central Region</t>
+  </si>
+  <si>
+    <t>Soybean Belt (productivity weighted)</t>
   </si>
   <si>
     <t>Upper Mississippi River Basin</t>
   </si>
   <si>
-    <t>Central Region</t>
-  </si>
-  <si>
-    <t>Ohio River Basin</t>
-  </si>
-  <si>
-    <t>East North Central Region</t>
-  </si>
-  <si>
-    <t>Tennessee River Basin</t>
-  </si>
-  <si>
-    <t>Soybean Belt (area weighted)</t>
-  </si>
-  <si>
-    <t>Soybean Belt (productivity weighted)</t>
+    <t>Great Lakes Basin</t>
   </si>
   <si>
     <t>Corn Belt (productivity weighted)</t>
   </si>
   <si>
+    <t>Primary Corn and Soybean Belt (area weighted)</t>
+  </si>
+  <si>
     <t>Corn Belt (area weighted)</t>
-  </si>
-  <si>
-    <t>Primary Corn and Soybean Belt (area weighted)</t>
-  </si>
-  <si>
-    <t>Great Lakes Basin</t>
   </si>
 </sst>
 </file>
@@ -582,25 +582,25 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>-0.02432762131113448</v>
+        <v>-0.0411354722684574</v>
       </c>
       <c r="D2">
-        <v>1.415886143931257</v>
+        <v>2.23467646388699</v>
       </c>
       <c r="E2">
-        <v>-0.3446370015062665</v>
+        <v>-0.3333016243544084</v>
       </c>
       <c r="F2">
-        <v>5.196572324590879E-05</v>
+        <v>9.415108394865852E-05</v>
       </c>
       <c r="G2">
-        <v>0.005811785210241171</v>
+        <v>0.01020554692577966</v>
       </c>
       <c r="H2">
         <v>132</v>
       </c>
       <c r="I2">
-        <v>-1.771032247827361</v>
+        <v>-3.154070403280929</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -611,25 +611,25 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>-0.01945959190133557</v>
+        <v>-0.0352902033014528</v>
       </c>
       <c r="D3">
-        <v>1.027330542264752</v>
+        <v>1.725043669780512</v>
       </c>
       <c r="E3">
-        <v>-0.2823142028973376</v>
+        <v>-0.2929204632665108</v>
       </c>
       <c r="F3">
-        <v>0.001039278185073925</v>
+        <v>0.0006532793352659417</v>
       </c>
       <c r="G3">
-        <v>0.005799542382940857</v>
+        <v>0.01010305717463023</v>
       </c>
       <c r="H3">
         <v>132</v>
       </c>
       <c r="I3">
-        <v>-1.521875996810207</v>
+        <v>-2.897972962709805</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -640,25 +640,25 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>-0.01928892227843327</v>
+        <v>-0.03526617550120965</v>
       </c>
       <c r="D4">
-        <v>0.892510808948779</v>
+        <v>1.706828434723171</v>
       </c>
       <c r="E4">
-        <v>-0.3071437752502773</v>
+        <v>-0.3086558322008021</v>
       </c>
       <c r="F4">
-        <v>0.0003406604466830479</v>
+        <v>0.0003172560921506166</v>
       </c>
       <c r="G4">
-        <v>0.005241768178813528</v>
+        <v>0.009531737530350609</v>
       </c>
       <c r="H4">
         <v>132</v>
       </c>
       <c r="I4">
-        <v>-1.634338009525979</v>
+        <v>-2.913040555935293</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -669,54 +669,54 @@
         <v>12</v>
       </c>
       <c r="C5">
-        <v>-0.01913348697161761</v>
+        <v>-0.03520095345929013</v>
       </c>
       <c r="D5">
-        <v>0.899510532283089</v>
+        <v>1.696293764714817</v>
       </c>
       <c r="E5">
-        <v>-0.3112432322757374</v>
+        <v>-0.3152409369066451</v>
       </c>
       <c r="F5">
-        <v>0.000280627563059138</v>
+        <v>0.0002316597770186524</v>
       </c>
       <c r="G5">
-        <v>0.005123858189402229</v>
+        <v>0.009294193172964838</v>
       </c>
       <c r="H5">
         <v>132</v>
       </c>
       <c r="I5">
-        <v>-1.606976260998818</v>
+        <v>-2.915031138452191</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
       </c>
       <c r="C6">
-        <v>-0.01822769039680593</v>
+        <v>-0.03204737207348697</v>
       </c>
       <c r="D6">
-        <v>0.8854847888118564</v>
+        <v>1.574683678894205</v>
       </c>
       <c r="E6">
-        <v>-0.300298609206779</v>
+        <v>-0.3046751323290404</v>
       </c>
       <c r="F6">
-        <v>0.000467956843911717</v>
+        <v>0.0003823272615800807</v>
       </c>
       <c r="G6">
-        <v>0.005077904910449293</v>
+        <v>0.008786760949171026</v>
       </c>
       <c r="H6">
         <v>132</v>
       </c>
       <c r="I6">
-        <v>-1.502342653169721</v>
+        <v>-2.623522062732588</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -727,170 +727,170 @@
         <v>14</v>
       </c>
       <c r="C7">
-        <v>-0.0176664258420414</v>
+        <v>-0.03195455675969939</v>
       </c>
       <c r="D7">
-        <v>0.9059306545584735</v>
+        <v>1.532669932406775</v>
       </c>
       <c r="E7">
-        <v>-0.2641617868229186</v>
+        <v>-0.2597776525681483</v>
       </c>
       <c r="F7">
-        <v>0.002208347953085169</v>
+        <v>0.00262930290905632</v>
       </c>
       <c r="G7">
-        <v>0.005657173821167904</v>
+        <v>0.01041807260689085</v>
       </c>
       <c r="H7">
         <v>132</v>
       </c>
       <c r="I7">
-        <v>-1.40837113074895</v>
+        <v>-2.653377003113846</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B8" t="s">
         <v>15</v>
       </c>
       <c r="C8">
-        <v>-0.01684107692896364</v>
+        <v>-0.02893448924184159</v>
       </c>
       <c r="D8">
-        <v>0.909334225715805</v>
+        <v>1.28316359079517</v>
       </c>
       <c r="E8">
-        <v>-0.2901983878392034</v>
+        <v>-0.2453709815336088</v>
       </c>
       <c r="F8">
-        <v>0.000737209477971219</v>
+        <v>0.004571527075236813</v>
       </c>
       <c r="G8">
-        <v>0.004870795837793727</v>
+        <v>0.01002621621496766</v>
       </c>
       <c r="H8">
         <v>132</v>
       </c>
       <c r="I8">
-        <v>-1.296846851978431</v>
+        <v>-2.507254499886079</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
         <v>16</v>
       </c>
       <c r="C9">
-        <v>-0.01563137793924684</v>
+        <v>-0.0288258467125482</v>
       </c>
       <c r="D9">
-        <v>0.7125836099990231</v>
+        <v>1.323648515227462</v>
       </c>
       <c r="E9">
-        <v>-0.295177691675999</v>
+        <v>-0.2627595316574345</v>
       </c>
       <c r="F9">
-        <v>0.0005904431683502271</v>
+        <v>0.002335826102821001</v>
       </c>
       <c r="G9">
-        <v>0.0044375836609449</v>
+        <v>0.009283608734072829</v>
       </c>
       <c r="H9">
         <v>132</v>
       </c>
       <c r="I9">
-        <v>-1.335126900042313</v>
+        <v>-2.452537404116351</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
         <v>17</v>
       </c>
       <c r="C10">
-        <v>-0.0153174185960589</v>
+        <v>-0.0266631272838585</v>
       </c>
       <c r="D10">
-        <v>0.5846897275656673</v>
+        <v>1.286056049213944</v>
       </c>
       <c r="E10">
-        <v>-0.2320707123795621</v>
+        <v>-0.2480729078390896</v>
       </c>
       <c r="F10">
-        <v>0.007415436113426153</v>
+        <v>0.00413069422733446</v>
       </c>
       <c r="G10">
-        <v>0.00563082463579716</v>
+        <v>0.009132042348967964</v>
       </c>
       <c r="H10">
         <v>132</v>
       </c>
       <c r="I10">
-        <v>-1.421892108518048</v>
+        <v>-2.20681362497152</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="B11" t="s">
         <v>18</v>
       </c>
       <c r="C11">
-        <v>-0.01022631582674343</v>
+        <v>-0.02229999878252189</v>
       </c>
       <c r="D11">
-        <v>1.237717806420814</v>
+        <v>1.639766081871345</v>
       </c>
       <c r="E11">
-        <v>-0.1374893682289229</v>
+        <v>-0.189072919740349</v>
       </c>
       <c r="F11">
-        <v>0.1159311063762488</v>
+        <v>0.02991266404030203</v>
       </c>
       <c r="G11">
-        <v>0.006461514308038088</v>
+        <v>0.01015778411385329</v>
       </c>
       <c r="H11">
         <v>132</v>
       </c>
       <c r="I11">
-        <v>-0.1019295668825746</v>
+        <v>-1.281533758639022</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="B12" t="s">
         <v>19</v>
       </c>
       <c r="C12">
-        <v>-0.01010860339606824</v>
+        <v>-0.02156327668581586</v>
       </c>
       <c r="D12">
-        <v>1.077164027492975</v>
+        <v>1.756839067365383</v>
       </c>
       <c r="E12">
-        <v>-0.1456800568582489</v>
+        <v>-0.1788056777407482</v>
       </c>
       <c r="F12">
-        <v>0.09556985056400732</v>
+        <v>0.04023346289031619</v>
       </c>
       <c r="G12">
-        <v>0.006020898807561757</v>
+        <v>0.01040652789521261</v>
       </c>
       <c r="H12">
         <v>132</v>
       </c>
       <c r="I12">
-        <v>-0.2470630173919643</v>
+        <v>-1.067950178476494</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -901,25 +901,25 @@
         <v>20</v>
       </c>
       <c r="C13">
-        <v>-0.009456711882313101</v>
+        <v>-0.02138517703001432</v>
       </c>
       <c r="D13">
-        <v>0.5021933079451877</v>
+        <v>1.066991721728564</v>
       </c>
       <c r="E13">
-        <v>-0.1499366195853837</v>
+        <v>-0.1836941160564479</v>
       </c>
       <c r="F13">
-        <v>0.08616743585440882</v>
+        <v>0.03499750618770796</v>
       </c>
       <c r="G13">
-        <v>0.00546919454870391</v>
+        <v>0.01003672756545275</v>
       </c>
       <c r="H13">
         <v>132</v>
       </c>
       <c r="I13">
-        <v>-0.7366359486378284</v>
+        <v>-1.734466469203312</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -930,402 +930,402 @@
         <v>21</v>
       </c>
       <c r="C14">
-        <v>-0.007935263644885981</v>
+        <v>-0.01813496266690321</v>
       </c>
       <c r="D14">
-        <v>1.077202950558214</v>
+        <v>1.574102680944787</v>
       </c>
       <c r="E14">
-        <v>-0.1042580027278117</v>
+        <v>-0.1482293828050319</v>
       </c>
       <c r="F14">
-        <v>0.234169978134209</v>
+        <v>0.08984579027600456</v>
       </c>
       <c r="G14">
-        <v>0.006639066664983406</v>
+        <v>0.01061173374494626</v>
       </c>
       <c r="H14">
         <v>132</v>
       </c>
       <c r="I14">
-        <v>0.03768341307815026</v>
+        <v>-0.8015774284195341</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B15" t="s">
         <v>22</v>
       </c>
       <c r="C15">
-        <v>-0.006602016715229136</v>
+        <v>-0.01797959506677867</v>
       </c>
       <c r="D15">
-        <v>0.1275114599268733</v>
+        <v>1.577461456671983</v>
       </c>
       <c r="E15">
-        <v>-0.1502074705681803</v>
+        <v>-0.1490747582267289</v>
       </c>
       <c r="F15">
-        <v>0.08559508068148967</v>
+        <v>0.08800905453118589</v>
       </c>
       <c r="G15">
-        <v>0.00381116680372573</v>
+        <v>0.01045981400991507</v>
       </c>
       <c r="H15">
         <v>132</v>
       </c>
       <c r="I15">
-        <v>-0.7373527297681435</v>
+        <v>-0.7778654970760233</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B16" t="s">
         <v>23</v>
       </c>
       <c r="C16">
-        <v>-0.005881797969196808</v>
+        <v>-0.01773532547538172</v>
       </c>
       <c r="D16">
-        <v>0.09319698054660452</v>
+        <v>0.6490628085364928</v>
       </c>
       <c r="E16">
-        <v>-0.1351099575783354</v>
+        <v>-0.1832944512485755</v>
       </c>
       <c r="F16">
-        <v>0.1224375902199461</v>
+        <v>0.03540282708742573</v>
       </c>
       <c r="G16">
-        <v>0.00378312319947942</v>
+        <v>0.008342521525153555</v>
       </c>
       <c r="H16">
         <v>132</v>
       </c>
       <c r="I16">
-        <v>-0.6773185534181774</v>
+        <v>-1.674264828738513</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B17" t="s">
         <v>24</v>
       </c>
       <c r="C17">
-        <v>-0.005845500971125145</v>
+        <v>-0.01692220662690731</v>
       </c>
       <c r="D17">
-        <v>0.9209854723388557</v>
+        <v>0.5876217057796005</v>
       </c>
       <c r="E17">
-        <v>-0.08272342168051398</v>
+        <v>-0.1746600056007663</v>
       </c>
       <c r="F17">
-        <v>0.3456821314224339</v>
+        <v>0.04517420194544366</v>
       </c>
       <c r="G17">
-        <v>0.006176329955170567</v>
+        <v>0.008366896259880434</v>
       </c>
       <c r="H17">
         <v>132</v>
       </c>
       <c r="I17">
-        <v>0.1552248451214618</v>
+        <v>-1.629187362345257</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="B18" t="s">
         <v>25</v>
       </c>
       <c r="C18">
-        <v>-0.003305504019789731</v>
+        <v>-0.01573270441892378</v>
       </c>
       <c r="D18">
-        <v>0.3763698206555346</v>
+        <v>0.6867547657021338</v>
       </c>
       <c r="E18">
-        <v>-0.05308685943464839</v>
+        <v>-0.1441713301930002</v>
       </c>
       <c r="F18">
-        <v>0.5454800249814635</v>
+        <v>0.09909104851227336</v>
       </c>
       <c r="G18">
-        <v>0.005453384862871473</v>
+        <v>0.009470910834615258</v>
       </c>
       <c r="H18">
         <v>132</v>
       </c>
       <c r="I18">
-        <v>-0.05665120593692002</v>
+        <v>-1.374229513176881</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="B19" t="s">
         <v>26</v>
       </c>
       <c r="C19">
-        <v>-0.002892945720601693</v>
+        <v>-0.01432202122238281</v>
       </c>
       <c r="D19">
-        <v>0.03410645119291741</v>
+        <v>0.5901883496620338</v>
       </c>
       <c r="E19">
-        <v>-0.05276028273298681</v>
+        <v>-0.1475612378927284</v>
       </c>
       <c r="F19">
-        <v>0.5479580270480264</v>
+        <v>0.09131893130778099</v>
       </c>
       <c r="G19">
-        <v>0.004802376339190134</v>
+        <v>0.008419375454507444</v>
       </c>
       <c r="H19">
         <v>132</v>
       </c>
       <c r="I19">
-        <v>-0.3448694382059043</v>
+        <v>-1.285996430470115</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B20" t="s">
         <v>27</v>
       </c>
       <c r="C20">
-        <v>-0.001785562100949805</v>
+        <v>-0.01411379767948671</v>
       </c>
       <c r="D20">
-        <v>0.3629012873091819</v>
+        <v>0.5843779904306219</v>
       </c>
       <c r="E20">
-        <v>-0.0282086555456899</v>
+        <v>-0.1458094443780715</v>
       </c>
       <c r="F20">
-        <v>0.7481541835109912</v>
+        <v>0.09527254496258719</v>
       </c>
       <c r="G20">
-        <v>0.005549425641083449</v>
+        <v>0.008398856049752473</v>
       </c>
       <c r="H20">
         <v>132</v>
       </c>
       <c r="I20">
-        <v>0.1289926520847574</v>
+        <v>-1.264529505582137</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B21" t="s">
         <v>28</v>
       </c>
       <c r="C21">
-        <v>-0.001522875357820546</v>
+        <v>-0.01367947975420856</v>
       </c>
       <c r="D21">
-        <v>-0.03684347502956518</v>
+        <v>0.8123190552137922</v>
       </c>
       <c r="E21">
-        <v>-0.03454603160556041</v>
+        <v>-0.126165011912703</v>
       </c>
       <c r="F21">
-        <v>0.6941377457387093</v>
+        <v>0.1494418698395061</v>
       </c>
       <c r="G21">
-        <v>0.003863983050234531</v>
+        <v>0.00943354014332011</v>
       </c>
       <c r="H21">
         <v>132</v>
       </c>
       <c r="I21">
-        <v>-0.2363401469040567</v>
+        <v>-0.9796927925875296</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B22" t="s">
         <v>29</v>
       </c>
       <c r="C22">
-        <v>-0.001120427406873483</v>
+        <v>-0.01287667468462968</v>
       </c>
       <c r="D22">
-        <v>-0.05878101639379842</v>
+        <v>0.8924625958836483</v>
       </c>
       <c r="E22">
-        <v>-0.02569057005428844</v>
+        <v>-0.114433583088871</v>
       </c>
       <c r="F22">
-        <v>0.7699784402870167</v>
+        <v>0.1913712291385143</v>
       </c>
       <c r="G22">
-        <v>0.003823797991450977</v>
+        <v>0.009804291515940264</v>
       </c>
       <c r="H22">
         <v>132</v>
       </c>
       <c r="I22">
-        <v>-0.2055570066942247</v>
+        <v>-0.7943817878028403</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="B23" t="s">
         <v>30</v>
       </c>
       <c r="C23">
-        <v>7.0817161372746E-05</v>
+        <v>-0.01187609029513409</v>
       </c>
       <c r="D23">
-        <v>-0.1969193682257589</v>
+        <v>1.334979873927242</v>
       </c>
       <c r="E23">
-        <v>0.001104913010624419</v>
+        <v>-0.1110657891395612</v>
       </c>
       <c r="F23">
-        <v>0.9899678656202902</v>
+        <v>0.2048556323625222</v>
       </c>
       <c r="G23">
-        <v>0.005621322291968473</v>
+        <v>0.009320220905794371</v>
       </c>
       <c r="H23">
         <v>132</v>
       </c>
       <c r="I23">
-        <v>-0.1876423200859292</v>
+        <v>-0.2207879547353233</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="B24" t="s">
         <v>31</v>
       </c>
       <c r="C24">
-        <v>0.001124727713504045</v>
+        <v>-0.01115954355006183</v>
       </c>
       <c r="D24">
-        <v>-0.1978516637915135</v>
+        <v>1.206859193438141</v>
       </c>
       <c r="E24">
-        <v>0.01832962620158892</v>
+        <v>-0.09772085324428717</v>
       </c>
       <c r="F24">
-        <v>0.8347558929972645</v>
+        <v>0.2649708804810821</v>
       </c>
       <c r="G24">
-        <v>0.005380828415623864</v>
+        <v>0.009967905733720243</v>
       </c>
       <c r="H24">
         <v>132</v>
       </c>
       <c r="I24">
-        <v>-0.05051233332248364</v>
+        <v>-0.2550410116199591</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="B25" t="s">
         <v>32</v>
       </c>
       <c r="C25">
-        <v>0.001450903766305822</v>
+        <v>-0.01087410580580528</v>
       </c>
       <c r="D25">
-        <v>0.6378346705508359</v>
+        <v>0.366774132300448</v>
       </c>
       <c r="E25">
-        <v>0.02478846493304429</v>
+        <v>-0.09809820729272492</v>
       </c>
       <c r="F25">
-        <v>0.7778420163914107</v>
+        <v>0.2631212233710434</v>
       </c>
       <c r="G25">
-        <v>0.005131966676236426</v>
+        <v>0.009675223892116112</v>
       </c>
       <c r="H25">
         <v>132</v>
       </c>
       <c r="I25">
-        <v>0.8279030639368985</v>
+        <v>-1.057733728260044</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="B26" t="s">
         <v>33</v>
       </c>
       <c r="C26">
-        <v>0.001928516393591293</v>
+        <v>-0.01057220601816825</v>
       </c>
       <c r="D26">
-        <v>0.5031699107075047</v>
+        <v>0.2447269689374951</v>
       </c>
       <c r="E26">
-        <v>0.03034626372838977</v>
+        <v>-0.09305658270802122</v>
       </c>
       <c r="F26">
-        <v>0.729782028375256</v>
+        <v>0.2885650738077679</v>
       </c>
       <c r="G26">
-        <v>0.005571169462697458</v>
+        <v>0.009921064197522346</v>
       </c>
       <c r="H26">
         <v>132</v>
       </c>
       <c r="I26">
-        <v>0.7558055582679641</v>
+        <v>-1.140232019442546</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="B27" t="s">
         <v>34</v>
       </c>
       <c r="C27">
-        <v>0.002394414520985721</v>
+        <v>-0.01050254887739822</v>
       </c>
       <c r="D27">
-        <v>0.2087872413718278</v>
+        <v>0.6389523050049366</v>
       </c>
       <c r="E27">
-        <v>0.03791893972143265</v>
+        <v>-0.1111079567903332</v>
       </c>
       <c r="F27">
-        <v>0.6659833502562904</v>
+        <v>0.20468268039904</v>
       </c>
       <c r="G27">
-        <v>0.005534253231034209</v>
+        <v>0.008239114002632152</v>
       </c>
       <c r="H27">
         <v>132</v>
       </c>
       <c r="I27">
-        <v>0.5224555436209573</v>
+        <v>-0.7368815979342296</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -1336,199 +1336,199 @@
         <v>35</v>
       </c>
       <c r="C28">
-        <v>0.002524165387693485</v>
+        <v>-0.008633606918058501</v>
       </c>
       <c r="D28">
-        <v>0.03168646725037685</v>
+        <v>0.6014103440419228</v>
       </c>
       <c r="E28">
-        <v>0.04246093291559161</v>
+        <v>-0.07922547184720101</v>
       </c>
       <c r="F28">
-        <v>0.6287995695246029</v>
+        <v>0.3665288776596969</v>
       </c>
       <c r="G28">
-        <v>0.005209124584377282</v>
+        <v>0.009527709409717132</v>
       </c>
       <c r="H28">
         <v>132</v>
       </c>
       <c r="I28">
-        <v>0.3623521330382234</v>
+        <v>-0.5295921622237408</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B29" t="s">
         <v>36</v>
       </c>
       <c r="C29">
-        <v>0.003067187647914274</v>
+        <v>-0.008609092126569027</v>
       </c>
       <c r="D29">
-        <v>0.219775615988022</v>
+        <v>0.4132137161084531</v>
       </c>
       <c r="E29">
-        <v>0.0477867326811777</v>
+        <v>-0.09155345366258191</v>
       </c>
       <c r="F29">
-        <v>0.5863610688139875</v>
+        <v>0.2964580450478347</v>
       </c>
       <c r="G29">
-        <v>0.005622958710568333</v>
+        <v>0.008212646702638878</v>
       </c>
       <c r="H29">
         <v>132</v>
       </c>
       <c r="I29">
-        <v>0.6215771978647919</v>
+        <v>-0.7145773524720894</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="B30" t="s">
         <v>37</v>
       </c>
       <c r="C30">
-        <v>0.003182950871279516</v>
+        <v>-0.006828086872281329</v>
       </c>
       <c r="D30">
-        <v>-0.0750931305536568</v>
+        <v>0.5589063568010937</v>
       </c>
       <c r="E30">
-        <v>0.07754897829123658</v>
+        <v>-0.06244807091648128</v>
       </c>
       <c r="F30">
-        <v>0.3767892499257416</v>
+        <v>0.4768708575531766</v>
       </c>
       <c r="G30">
-        <v>0.003588990813391112</v>
+        <v>0.009571055986333487</v>
       </c>
       <c r="H30">
         <v>132</v>
       </c>
       <c r="I30">
-        <v>0.3418734335839598</v>
+        <v>-0.3355730234677604</v>
       </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="B31" t="s">
         <v>38</v>
       </c>
       <c r="C31">
-        <v>0.003985777681539031</v>
+        <v>-0.006594826761560389</v>
       </c>
       <c r="D31">
-        <v>-0.3222489936963621</v>
+        <v>0.5786530720741246</v>
       </c>
       <c r="E31">
-        <v>0.06511656283518528</v>
+        <v>-0.05964547561245233</v>
       </c>
       <c r="F31">
-        <v>0.4582058040425409</v>
+        <v>0.4969086795356665</v>
       </c>
       <c r="G31">
-        <v>0.005357068854497813</v>
+        <v>0.009680110453125093</v>
       </c>
       <c r="H31">
         <v>132</v>
       </c>
       <c r="I31">
-        <v>0.199887882585251</v>
+        <v>-0.2852692336902863</v>
       </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="B32" t="s">
         <v>39</v>
       </c>
       <c r="C32">
-        <v>0.004503762752772682</v>
+        <v>-0.006296440267914754</v>
       </c>
       <c r="D32">
-        <v>-0.261628855689006</v>
+        <v>0.1308259284575073</v>
       </c>
       <c r="E32">
-        <v>0.1099536467526136</v>
+        <v>-0.05635723434182606</v>
       </c>
       <c r="F32">
-        <v>0.2094550952611545</v>
+        <v>0.5209723530609345</v>
       </c>
       <c r="G32">
-        <v>0.003570696391181251</v>
+        <v>0.00978324550125702</v>
       </c>
       <c r="H32">
         <v>132</v>
       </c>
       <c r="I32">
-        <v>0.3283640649242153</v>
+        <v>-0.6940077466393255</v>
       </c>
     </row>
     <row r="33" spans="1:9">
       <c r="A33">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="B33" t="s">
         <v>40</v>
       </c>
       <c r="C33">
-        <v>0.005263987146412676</v>
+        <v>-0.005284602902119976</v>
       </c>
       <c r="D33">
-        <v>-0.521254000802873</v>
+        <v>0.2007879547353231</v>
       </c>
       <c r="E33">
-        <v>0.08618868425799737</v>
+        <v>-0.05665944660199716</v>
       </c>
       <c r="F33">
-        <v>0.3257825547070974</v>
+        <v>0.5187362479634727</v>
       </c>
       <c r="G33">
-        <v>0.005336712363329088</v>
+        <v>0.008167142378774948</v>
       </c>
       <c r="H33">
         <v>132</v>
       </c>
       <c r="I33">
-        <v>0.1683283153771875</v>
+        <v>-0.4914950254423938</v>
       </c>
     </row>
     <row r="34" spans="1:9">
       <c r="A34">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="B34" t="s">
         <v>41</v>
       </c>
       <c r="C34">
-        <v>0.007400828332355625</v>
+        <v>-0.004926699121154723</v>
       </c>
       <c r="D34">
-        <v>-0.4329180364330741</v>
+        <v>-0.1323012075643655</v>
       </c>
       <c r="E34">
-        <v>0.179185119913361</v>
+        <v>-0.04397648034132051</v>
       </c>
       <c r="F34">
-        <v>0.03980479975544905</v>
+        <v>0.6165906652984592</v>
       </c>
       <c r="G34">
-        <v>0.003563857399385715</v>
+        <v>0.009816203249694235</v>
       </c>
       <c r="H34">
         <v>132</v>
       </c>
       <c r="I34">
-        <v>0.5365904751055127</v>
+        <v>-0.7776987924356342</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -1539,170 +1539,170 @@
         <v>42</v>
       </c>
       <c r="C35">
-        <v>0.008027356236332878</v>
+        <v>-0.004068203124048844</v>
       </c>
       <c r="D35">
-        <v>-0.04816737460534465</v>
+        <v>0.4898006379585327</v>
       </c>
       <c r="E35">
-        <v>0.1399210604435986</v>
+        <v>-0.03918754294533208</v>
       </c>
       <c r="F35">
-        <v>0.1095624785634914</v>
+        <v>0.6555107224077463</v>
       </c>
       <c r="G35">
-        <v>0.004982236255722181</v>
+        <v>0.009098068394422568</v>
       </c>
       <c r="H35">
         <v>132</v>
       </c>
       <c r="I35">
-        <v>1.003416292354262</v>
+        <v>-0.0431339712918658</v>
       </c>
     </row>
     <row r="36" spans="1:9">
       <c r="A36">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="B36" t="s">
         <v>43</v>
       </c>
       <c r="C36">
-        <v>0.008641476733868971</v>
+        <v>-0.002966950686918545</v>
       </c>
       <c r="D36">
-        <v>0.0396750127483213</v>
+        <v>-0.1173061441482494</v>
       </c>
       <c r="E36">
-        <v>0.140202418142593</v>
+        <v>-0.03074025988486126</v>
       </c>
       <c r="F36">
-        <v>0.1088435978876417</v>
+        <v>0.7264120542100554</v>
       </c>
       <c r="G36">
-        <v>0.005352416159203851</v>
+        <v>0.008461080438517623</v>
       </c>
       <c r="H36">
         <v>132</v>
       </c>
       <c r="I36">
-        <v>1.171708464885156</v>
+        <v>-0.5059766841345789</v>
       </c>
     </row>
     <row r="37" spans="1:9">
       <c r="A37">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B37" t="s">
         <v>44</v>
       </c>
       <c r="C37">
-        <v>0.008680379818387051</v>
+        <v>-0.00294691447564087</v>
       </c>
       <c r="D37">
-        <v>-0.5170623528518266</v>
+        <v>0.5076946153261943</v>
       </c>
       <c r="E37">
-        <v>0.2163677302268636</v>
+        <v>-0.02809305680631405</v>
       </c>
       <c r="F37">
-        <v>0.01270892466457198</v>
+        <v>0.7491518704807886</v>
       </c>
       <c r="G37">
-        <v>0.003435288093108453</v>
+        <v>0.009196560113991408</v>
       </c>
       <c r="H37">
         <v>132</v>
       </c>
       <c r="I37">
-        <v>0.6200674033568772</v>
+        <v>0.1216488190172403</v>
       </c>
     </row>
     <row r="38" spans="1:9">
       <c r="A38">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="B38" t="s">
         <v>45</v>
       </c>
       <c r="C38">
-        <v>0.008919664582294436</v>
+        <v>-0.002851142429286262</v>
       </c>
       <c r="D38">
-        <v>-0.7076759810782365</v>
+        <v>0.05897205134047243</v>
       </c>
       <c r="E38">
-        <v>0.2058950056160263</v>
+        <v>-0.03096541320688597</v>
       </c>
       <c r="F38">
-        <v>0.01786087572562975</v>
+        <v>0.7244885888321929</v>
       </c>
       <c r="G38">
-        <v>0.003718131513396382</v>
+        <v>0.008071644839952213</v>
       </c>
       <c r="H38">
         <v>132</v>
       </c>
       <c r="I38">
-        <v>0.4608000792023346</v>
+        <v>-0.3145276068960279</v>
       </c>
     </row>
     <row r="39" spans="1:9">
       <c r="A39">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B39" t="s">
         <v>46</v>
       </c>
       <c r="C39">
-        <v>0.01122392422764057</v>
+        <v>-0.002153197010569448</v>
       </c>
       <c r="D39">
-        <v>-0.2167137540821747</v>
+        <v>0.1977515759094706</v>
       </c>
       <c r="E39">
-        <v>0.2156534134120091</v>
+        <v>-0.02259394731379443</v>
       </c>
       <c r="F39">
-        <v>0.01301358610784453</v>
+        <v>0.7970640964337743</v>
       </c>
       <c r="G39">
-        <v>0.004457338387956868</v>
+        <v>0.00835620529743869</v>
       </c>
       <c r="H39">
         <v>132</v>
       </c>
       <c r="I39">
-        <v>1.253620319738741</v>
+        <v>-0.08431723247512707</v>
       </c>
     </row>
     <row r="40" spans="1:9">
       <c r="A40">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="B40" t="s">
         <v>47</v>
       </c>
       <c r="C40">
-        <v>0.0114411825762483</v>
+        <v>0.001037552242855583</v>
       </c>
       <c r="D40">
-        <v>-0.5624773649491697</v>
+        <v>0.1631514392040704</v>
       </c>
       <c r="E40">
-        <v>0.2279461982762683</v>
+        <v>0.01028862491811455</v>
       </c>
       <c r="F40">
-        <v>0.008571335159172629</v>
+        <v>0.906791824942129</v>
       </c>
       <c r="G40">
-        <v>0.004286278036918134</v>
+        <v>0.008844188188090357</v>
       </c>
       <c r="H40">
         <v>132</v>
       </c>
       <c r="I40">
-        <v>0.9363175525393572</v>
+        <v>0.2990707830181517</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -1713,25 +1713,25 @@
         <v>48</v>
       </c>
       <c r="C41">
-        <v>0.01192946211319913</v>
+        <v>0.001384507417050609</v>
       </c>
       <c r="D41">
-        <v>-0.5980473369571115</v>
+        <v>-0.1369226095541886</v>
       </c>
       <c r="E41">
-        <v>0.2522396289735322</v>
+        <v>0.01468070963807188</v>
       </c>
       <c r="F41">
-        <v>0.003525307083490222</v>
+        <v>0.8673123989627762</v>
       </c>
       <c r="G41">
-        <v>0.00401384697698999</v>
+        <v>0.008270461725503534</v>
       </c>
       <c r="H41">
         <v>132</v>
       </c>
       <c r="I41">
-        <v>0.9647121998719743</v>
+        <v>0.04444786207944121</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -1742,170 +1742,170 @@
         <v>49</v>
       </c>
       <c r="C42">
-        <v>0.01196220916870346</v>
+        <v>0.001430562874918037</v>
       </c>
       <c r="D42">
-        <v>-0.36715114355152</v>
+        <v>0.07430318219791907</v>
       </c>
       <c r="E42">
-        <v>0.2397876251091137</v>
+        <v>0.01492319343911611</v>
       </c>
       <c r="F42">
-        <v>0.005618225344387926</v>
+        <v>0.8651413545556252</v>
       </c>
       <c r="G42">
-        <v>0.004247702240765017</v>
+        <v>0.008406692096321463</v>
       </c>
       <c r="H42">
         <v>132</v>
       </c>
       <c r="I42">
-        <v>1.199898257548634</v>
+        <v>0.2617069188121819</v>
       </c>
     </row>
     <row r="43" spans="1:9">
       <c r="A43">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="B43" t="s">
         <v>50</v>
       </c>
       <c r="C43">
-        <v>0.01201995490113208</v>
+        <v>0.001455642924104156</v>
       </c>
       <c r="D43">
-        <v>-0.6565936621857675</v>
+        <v>-0.1581476418318525</v>
       </c>
       <c r="E43">
-        <v>0.2556371547309814</v>
+        <v>0.01501991369395063</v>
       </c>
       <c r="F43">
-        <v>0.003092079629777928</v>
+        <v>0.8642756630945414</v>
       </c>
       <c r="G43">
-        <v>0.003986865728972572</v>
+        <v>0.008498978817353163</v>
       </c>
       <c r="H43">
         <v>132</v>
       </c>
       <c r="I43">
-        <v>0.918020429862535</v>
+        <v>0.03254158122579193</v>
       </c>
     </row>
     <row r="44" spans="1:9">
       <c r="A44">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B44" t="s">
         <v>51</v>
       </c>
       <c r="C44">
-        <v>0.01237652628895526</v>
+        <v>0.001921763117022257</v>
       </c>
       <c r="D44">
-        <v>-0.3187532006422984</v>
+        <v>0.04056390977443614</v>
       </c>
       <c r="E44">
-        <v>0.2219217905598667</v>
+        <v>0.0191233388026769</v>
       </c>
       <c r="F44">
-        <v>0.01054550613810886</v>
+        <v>0.8277091309594644</v>
       </c>
       <c r="G44">
-        <v>0.004769364073213885</v>
+        <v>0.008812213950588928</v>
       </c>
       <c r="H44">
         <v>132</v>
       </c>
       <c r="I44">
-        <v>1.302571743210841</v>
+        <v>0.2923148781043519</v>
       </c>
     </row>
     <row r="45" spans="1:9">
       <c r="A45">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="B45" t="s">
         <v>52</v>
       </c>
       <c r="C45">
-        <v>0.0127719982766473</v>
+        <v>0.00196434876225957</v>
       </c>
       <c r="D45">
-        <v>-0.39334077889529</v>
+        <v>0.1308806106174527</v>
       </c>
       <c r="E45">
-        <v>0.2312596076419597</v>
+        <v>0.02006847456823961</v>
       </c>
       <c r="F45">
-        <v>0.007631174355192349</v>
+        <v>0.819335891069599</v>
       </c>
       <c r="G45">
-        <v>0.004712507531929267</v>
+        <v>0.008583118068236929</v>
       </c>
       <c r="H45">
         <v>132</v>
       </c>
       <c r="I45">
-        <v>1.279790995345506</v>
+        <v>0.3882102984734564</v>
       </c>
     </row>
     <row r="46" spans="1:9">
       <c r="A46">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="B46" t="s">
         <v>53</v>
       </c>
       <c r="C46">
-        <v>0.01281018081289275</v>
+        <v>0.00249411697181886</v>
       </c>
       <c r="D46">
-        <v>-0.3157271967798284</v>
+        <v>-0.1374808232702968</v>
       </c>
       <c r="E46">
-        <v>0.2182521254524658</v>
+        <v>0.02782030399491411</v>
       </c>
       <c r="F46">
-        <v>0.01193496712084789</v>
+        <v>0.7515075345951464</v>
       </c>
       <c r="G46">
-        <v>0.005023738733955732</v>
+        <v>0.007859865961632004</v>
       </c>
       <c r="H46">
         <v>132</v>
       </c>
       <c r="I46">
-        <v>1.362406489709121</v>
+        <v>0.1892485000379738</v>
       </c>
     </row>
     <row r="47" spans="1:9">
       <c r="A47">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B47" t="s">
         <v>54</v>
       </c>
       <c r="C47">
-        <v>0.01327224916410188</v>
+        <v>0.002500126095947712</v>
       </c>
       <c r="D47">
-        <v>-0.2612271615185149</v>
+        <v>0.0704841649578492</v>
       </c>
       <c r="E47">
-        <v>0.2246138359705911</v>
+        <v>0.02449216862982284</v>
       </c>
       <c r="F47">
-        <v>0.009618675238965251</v>
+        <v>0.7804297643586061</v>
       </c>
       <c r="G47">
-        <v>0.005050041531968662</v>
+        <v>0.008950199127191827</v>
       </c>
       <c r="H47">
         <v>132</v>
       </c>
       <c r="I47">
-        <v>1.477437478978832</v>
+        <v>0.3980006835269995</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -1916,54 +1916,54 @@
         <v>55</v>
       </c>
       <c r="C48">
-        <v>0.01349801743627434</v>
+        <v>0.002681278143311087</v>
       </c>
       <c r="D48">
-        <v>-0.4451058924367195</v>
+        <v>-0.01746715273031055</v>
       </c>
       <c r="E48">
-        <v>0.2531275430923665</v>
+        <v>0.02698610153812701</v>
       </c>
       <c r="F48">
-        <v>0.00340711171675058</v>
+        <v>0.7587263608606799</v>
       </c>
       <c r="G48">
-        <v>0.004524595556054926</v>
+        <v>0.008711076881736727</v>
       </c>
       <c r="H48">
         <v>132</v>
       </c>
       <c r="I48">
-        <v>1.323134391715219</v>
+        <v>0.3337802840434418</v>
       </c>
     </row>
     <row r="49" spans="1:9">
       <c r="A49">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="B49" t="s">
         <v>56</v>
       </c>
       <c r="C49">
-        <v>0.01523191249910242</v>
+        <v>0.003696063545400631</v>
       </c>
       <c r="D49">
-        <v>-0.7420309974069372</v>
+        <v>0.02828662565504658</v>
       </c>
       <c r="E49">
-        <v>0.3444336309656957</v>
+        <v>0.03657209311020083</v>
       </c>
       <c r="F49">
-        <v>5.253345482818097E-05</v>
+        <v>0.6771727466291382</v>
       </c>
       <c r="G49">
-        <v>0.003641289652121534</v>
+        <v>0.00885782923737352</v>
       </c>
       <c r="H49">
         <v>132</v>
       </c>
       <c r="I49">
-        <v>1.25334953997548</v>
+        <v>0.5124709501025292</v>
       </c>
     </row>
   </sheetData>

--- a/output/palmer_drought_trendlines/region/Year.xlsx
+++ b/output/palmer_drought_trendlines/region/Year.xlsx
@@ -55,30 +55,30 @@
     <t>West Region</t>
   </si>
   <si>
+    <t>Great Basin</t>
+  </si>
+  <si>
     <t>California River Basin</t>
   </si>
   <si>
-    <t>Great Basin</t>
+    <t>US Rockies and Westward</t>
   </si>
   <si>
     <t>Rio Grande River Basin</t>
   </si>
   <si>
-    <t>US Rockies and Westward</t>
-  </si>
-  <si>
     <t>NWS Western Region</t>
   </si>
   <si>
     <t>Spring Wheat Belt (area weighted)</t>
   </si>
   <si>
+    <t>Cotton Belt (area weighted)</t>
+  </si>
+  <si>
     <t>West North Central Region</t>
   </si>
   <si>
-    <t>Cotton Belt (area weighted)</t>
-  </si>
-  <si>
     <t>Missouri River Basin</t>
   </si>
   <si>
@@ -109,12 +109,12 @@
     <t>Souris-Red-Rainy Basin</t>
   </si>
   <si>
+    <t>NWS Southern Region</t>
+  </si>
+  <si>
     <t>Spring Wheat Belt (productivity weighted)</t>
   </si>
   <si>
-    <t>NWS Southern Region</t>
-  </si>
-  <si>
     <t>Southern Plains and Gulf Coast</t>
   </si>
   <si>
@@ -163,25 +163,25 @@
     <t>Ohio River Basin</t>
   </si>
   <si>
+    <t>Central Region</t>
+  </si>
+  <si>
     <t>East North Central Region</t>
   </si>
   <si>
-    <t>Central Region</t>
-  </si>
-  <si>
     <t>Soybean Belt (productivity weighted)</t>
   </si>
   <si>
     <t>Upper Mississippi River Basin</t>
   </si>
   <si>
+    <t>Corn Belt (productivity weighted)</t>
+  </si>
+  <si>
+    <t>Primary Corn and Soybean Belt (area weighted)</t>
+  </si>
+  <si>
     <t>Great Lakes Basin</t>
-  </si>
-  <si>
-    <t>Corn Belt (productivity weighted)</t>
-  </si>
-  <si>
-    <t>Primary Corn and Soybean Belt (area weighted)</t>
   </si>
   <si>
     <t>Corn Belt (area weighted)</t>
@@ -582,25 +582,25 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>-0.0411354722684574</v>
+        <v>-0.03080453127962167</v>
       </c>
       <c r="D2">
-        <v>2.23467646388699</v>
+        <v>1.787002354370775</v>
       </c>
       <c r="E2">
-        <v>-0.3333016243544084</v>
+        <v>-0.3524734739731858</v>
       </c>
       <c r="F2">
-        <v>9.415108394865852E-05</v>
+        <v>3.399285706194627E-05</v>
       </c>
       <c r="G2">
-        <v>0.01020554692577966</v>
+        <v>0.007173145661646157</v>
       </c>
       <c r="H2">
         <v>132</v>
       </c>
       <c r="I2">
-        <v>-3.154070403280929</v>
+        <v>-2.248391243259664</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -611,25 +611,25 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>-0.0352902033014528</v>
+        <v>-0.02495242704262391</v>
       </c>
       <c r="D3">
-        <v>1.725043669780512</v>
+        <v>1.27707336523126</v>
       </c>
       <c r="E3">
-        <v>-0.2929204632665108</v>
+        <v>-0.29885016201052</v>
       </c>
       <c r="F3">
-        <v>0.0006532793352659417</v>
+        <v>0.0004999813631114843</v>
       </c>
       <c r="G3">
-        <v>0.01010305717463023</v>
+        <v>0.00698831653591923</v>
       </c>
       <c r="H3">
         <v>132</v>
       </c>
       <c r="I3">
-        <v>-2.897972962709805</v>
+        <v>-1.991694577352472</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -640,25 +640,25 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>-0.03526617550120965</v>
+        <v>-0.02463733066183849</v>
       </c>
       <c r="D4">
-        <v>1.706828434723171</v>
+        <v>1.246245158350421</v>
       </c>
       <c r="E4">
-        <v>-0.3086558322008021</v>
+        <v>-0.3182164267356593</v>
       </c>
       <c r="F4">
-        <v>0.0003172560921506166</v>
+        <v>0.0002004953218468969</v>
       </c>
       <c r="G4">
-        <v>0.009531737530350609</v>
+        <v>0.006437481702546875</v>
       </c>
       <c r="H4">
         <v>132</v>
       </c>
       <c r="I4">
-        <v>-2.913040555935293</v>
+        <v>-1.981245158350421</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -669,141 +669,141 @@
         <v>12</v>
       </c>
       <c r="C5">
-        <v>-0.03520095345929013</v>
+        <v>-0.02425996462356447</v>
       </c>
       <c r="D5">
-        <v>1.696293764714817</v>
+        <v>1.222184248500038</v>
       </c>
       <c r="E5">
-        <v>-0.3152409369066451</v>
+        <v>-0.3141177781915914</v>
       </c>
       <c r="F5">
-        <v>0.0002316597770186524</v>
+        <v>0.0002445491985007213</v>
       </c>
       <c r="G5">
-        <v>0.009294193172964838</v>
+        <v>0.00643084272576662</v>
       </c>
       <c r="H5">
         <v>132</v>
       </c>
       <c r="I5">
-        <v>-2.915031138452191</v>
+        <v>-1.955871117186907</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
       </c>
       <c r="C6">
-        <v>-0.03204737207348697</v>
+        <v>-0.02153247883762146</v>
       </c>
       <c r="D6">
-        <v>1.574683678894205</v>
+        <v>1.081046555783398</v>
       </c>
       <c r="E6">
-        <v>-0.3046751323290404</v>
+        <v>-0.2451693308370661</v>
       </c>
       <c r="F6">
-        <v>0.0003823272615800807</v>
+        <v>0.004606057634840167</v>
       </c>
       <c r="G6">
-        <v>0.008786760949171026</v>
+        <v>0.007467843147308669</v>
       </c>
       <c r="H6">
         <v>132</v>
       </c>
       <c r="I6">
-        <v>-2.623522062732588</v>
+        <v>-1.739708171945014</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7">
-        <v>-0.03195455675969939</v>
+        <v>-0.02102891684450544</v>
       </c>
       <c r="D7">
-        <v>1.532669932406775</v>
+        <v>1.097217285638338</v>
       </c>
       <c r="E7">
-        <v>-0.2597776525681483</v>
+        <v>-0.3075337510937151</v>
       </c>
       <c r="F7">
-        <v>0.00262930290905632</v>
+        <v>0.0003344760629451606</v>
       </c>
       <c r="G7">
-        <v>0.01041807260689085</v>
+        <v>0.005706610107774551</v>
       </c>
       <c r="H7">
         <v>132</v>
       </c>
       <c r="I7">
-        <v>-2.653377003113846</v>
+        <v>-1.657570820991874</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
         <v>15</v>
       </c>
       <c r="C8">
-        <v>-0.02893448924184159</v>
+        <v>-0.01814288931906449</v>
       </c>
       <c r="D8">
-        <v>1.28316359079517</v>
+        <v>0.8607203615098352</v>
       </c>
       <c r="E8">
-        <v>-0.2453709815336088</v>
+        <v>-0.2551789865088269</v>
       </c>
       <c r="F8">
-        <v>0.004571527075236813</v>
+        <v>0.00314755663346177</v>
       </c>
       <c r="G8">
-        <v>0.01002621621496766</v>
+        <v>0.006029324483437407</v>
       </c>
       <c r="H8">
         <v>132</v>
       </c>
       <c r="I8">
-        <v>-2.507254499886079</v>
+        <v>-1.515998139287613</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
         <v>16</v>
       </c>
       <c r="C9">
-        <v>-0.0288258467125482</v>
+        <v>-0.0181319146234775</v>
       </c>
       <c r="D9">
-        <v>1.323648515227462</v>
+        <v>0.8150520239993925</v>
       </c>
       <c r="E9">
-        <v>-0.2627595316574345</v>
+        <v>-0.2144148952271814</v>
       </c>
       <c r="F9">
-        <v>0.002335826102821001</v>
+        <v>0.01355697377267449</v>
       </c>
       <c r="G9">
-        <v>0.009283608734072829</v>
+        <v>0.007244312894839225</v>
       </c>
       <c r="H9">
         <v>132</v>
       </c>
       <c r="I9">
-        <v>-2.452537404116351</v>
+        <v>-1.56022879167616</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -814,25 +814,25 @@
         <v>17</v>
       </c>
       <c r="C10">
-        <v>-0.0266631272838585</v>
+        <v>-0.01584574291384256</v>
       </c>
       <c r="D10">
-        <v>1.286056049213944</v>
+        <v>0.8173027265132531</v>
       </c>
       <c r="E10">
-        <v>-0.2480729078390896</v>
+        <v>-0.2293293108474122</v>
       </c>
       <c r="F10">
-        <v>0.00413069422733446</v>
+        <v>0.008167108507095731</v>
       </c>
       <c r="G10">
-        <v>0.009132042348967964</v>
+        <v>0.005898612986249532</v>
       </c>
       <c r="H10">
         <v>132</v>
       </c>
       <c r="I10">
-        <v>-2.20681362497152</v>
+        <v>-1.258489595200122</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -843,83 +843,83 @@
         <v>18</v>
       </c>
       <c r="C11">
-        <v>-0.02229999878252189</v>
+        <v>-0.01142565382922956</v>
       </c>
       <c r="D11">
-        <v>1.639766081871345</v>
+        <v>1.168544467228678</v>
       </c>
       <c r="E11">
-        <v>-0.189072919740349</v>
+        <v>-0.136339179318471</v>
       </c>
       <c r="F11">
-        <v>0.02991266404030203</v>
+        <v>0.1190419339847311</v>
       </c>
       <c r="G11">
-        <v>0.01015778411385329</v>
+        <v>0.007281390282753626</v>
       </c>
       <c r="H11">
         <v>132</v>
       </c>
       <c r="I11">
-        <v>-1.281533758639022</v>
+        <v>-0.3282161844003952</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="B12" t="s">
         <v>19</v>
       </c>
       <c r="C12">
-        <v>-0.02156327668581586</v>
+        <v>-0.01105024880034924</v>
       </c>
       <c r="D12">
-        <v>1.756839067365383</v>
+        <v>0.6191448317764107</v>
       </c>
       <c r="E12">
-        <v>-0.1788056777407482</v>
+        <v>-0.1435532766604663</v>
       </c>
       <c r="F12">
-        <v>0.04023346289031619</v>
+        <v>0.1005627363232344</v>
       </c>
       <c r="G12">
-        <v>0.01040652789521261</v>
+        <v>0.006681371923880788</v>
       </c>
       <c r="H12">
         <v>132</v>
       </c>
       <c r="I12">
-        <v>-1.067950178476494</v>
+        <v>-0.82843776106934</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="B13" t="s">
         <v>20</v>
       </c>
       <c r="C13">
-        <v>-0.02138517703001432</v>
+        <v>-0.0106689955283768</v>
       </c>
       <c r="D13">
-        <v>1.066991721728564</v>
+        <v>1.284753550543024</v>
       </c>
       <c r="E13">
-        <v>-0.1836941160564479</v>
+        <v>-0.1220893482232191</v>
       </c>
       <c r="F13">
-        <v>0.03499750618770796</v>
+        <v>0.1631421281341393</v>
       </c>
       <c r="G13">
-        <v>0.01003672756545275</v>
+        <v>0.007606992021617731</v>
       </c>
       <c r="H13">
         <v>132</v>
       </c>
       <c r="I13">
-        <v>-1.734466469203312</v>
+        <v>-0.1128848636743371</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -930,25 +930,25 @@
         <v>21</v>
       </c>
       <c r="C14">
-        <v>-0.01813496266690321</v>
+        <v>-0.007315299873556203</v>
       </c>
       <c r="D14">
-        <v>1.574102680944787</v>
+        <v>1.105250626566416</v>
       </c>
       <c r="E14">
-        <v>-0.1482293828050319</v>
+        <v>-0.08222818181038635</v>
       </c>
       <c r="F14">
-        <v>0.08984579027600456</v>
+        <v>0.3485873472151525</v>
       </c>
       <c r="G14">
-        <v>0.01061173374494626</v>
+        <v>0.007776184361370478</v>
       </c>
       <c r="H14">
         <v>132</v>
       </c>
       <c r="I14">
-        <v>-0.8015774284195341</v>
+        <v>0.1469463431305538</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -959,25 +959,25 @@
         <v>22</v>
       </c>
       <c r="C15">
-        <v>-0.01797959506677867</v>
+        <v>-0.00716619793759207</v>
       </c>
       <c r="D15">
-        <v>1.577461456671983</v>
+        <v>1.10888091440723</v>
       </c>
       <c r="E15">
-        <v>-0.1490747582267289</v>
+        <v>-0.08287402698716127</v>
       </c>
       <c r="F15">
-        <v>0.08800905453118589</v>
+        <v>0.3448016716743351</v>
       </c>
       <c r="G15">
-        <v>0.01045981400991507</v>
+        <v>0.007557917483894821</v>
       </c>
       <c r="H15">
         <v>132</v>
       </c>
       <c r="I15">
-        <v>-0.7778654970760233</v>
+        <v>0.1701089845826689</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -988,25 +988,25 @@
         <v>23</v>
       </c>
       <c r="C16">
-        <v>-0.01773532547538172</v>
+        <v>-0.006764717136352331</v>
       </c>
       <c r="D16">
-        <v>0.6490628085364928</v>
+        <v>0.1736697805118858</v>
       </c>
       <c r="E16">
-        <v>-0.1832944512485755</v>
+        <v>-0.1260376193414514</v>
       </c>
       <c r="F16">
-        <v>0.03540282708742573</v>
+        <v>0.1498565258798243</v>
       </c>
       <c r="G16">
-        <v>0.008342521525153555</v>
+        <v>0.004669824866010369</v>
       </c>
       <c r="H16">
         <v>132</v>
       </c>
       <c r="I16">
-        <v>-1.674264828738513</v>
+        <v>-0.7125081643502695</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -1017,25 +1017,25 @@
         <v>24</v>
       </c>
       <c r="C17">
-        <v>-0.01692220662690731</v>
+        <v>-0.005981787397014395</v>
       </c>
       <c r="D17">
-        <v>0.5876217057796005</v>
+        <v>0.1135368724842409</v>
       </c>
       <c r="E17">
-        <v>-0.1746600056007663</v>
+        <v>-0.112002345666142</v>
       </c>
       <c r="F17">
-        <v>0.04517420194544366</v>
+        <v>0.2010390075968846</v>
       </c>
       <c r="G17">
-        <v>0.008366896259880434</v>
+        <v>0.004654691902682848</v>
       </c>
       <c r="H17">
         <v>132</v>
       </c>
       <c r="I17">
-        <v>-1.629187362345257</v>
+        <v>-0.6700772765246448</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -1046,25 +1046,25 @@
         <v>25</v>
       </c>
       <c r="C18">
-        <v>-0.01573270441892378</v>
+        <v>-0.005296955956859532</v>
       </c>
       <c r="D18">
-        <v>0.6867547657021338</v>
+        <v>0.2345389990126832</v>
       </c>
       <c r="E18">
-        <v>-0.1441713301930002</v>
+        <v>-0.07945730675063521</v>
       </c>
       <c r="F18">
-        <v>0.09909104851227336</v>
+        <v>0.3651236968978311</v>
       </c>
       <c r="G18">
-        <v>0.009470910834615258</v>
+        <v>0.005828348984753129</v>
       </c>
       <c r="H18">
         <v>132</v>
       </c>
       <c r="I18">
-        <v>-1.374229513176881</v>
+        <v>-0.4593622313359155</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -1075,25 +1075,25 @@
         <v>26</v>
       </c>
       <c r="C19">
-        <v>-0.01432202122238281</v>
+        <v>-0.003331476679206692</v>
       </c>
       <c r="D19">
-        <v>0.5901883496620338</v>
+        <v>0.1139314194577352</v>
       </c>
       <c r="E19">
-        <v>-0.1475612378927284</v>
+        <v>-0.0616457306889466</v>
       </c>
       <c r="F19">
-        <v>0.09131893130778099</v>
+        <v>0.482562305384543</v>
       </c>
       <c r="G19">
-        <v>0.008419375454507444</v>
+        <v>0.004730808000929614</v>
       </c>
       <c r="H19">
         <v>132</v>
       </c>
       <c r="I19">
-        <v>-1.285996430470115</v>
+        <v>-0.3224920255183413</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -1104,25 +1104,25 @@
         <v>27</v>
       </c>
       <c r="C20">
-        <v>-0.01411379767948671</v>
+        <v>-0.003078823881355018</v>
       </c>
       <c r="D20">
-        <v>0.5843779904306219</v>
+        <v>0.106195792511582</v>
       </c>
       <c r="E20">
-        <v>-0.1458094443780715</v>
+        <v>-0.05668368506776767</v>
       </c>
       <c r="F20">
-        <v>0.09527254496258719</v>
+        <v>0.5185571171664454</v>
       </c>
       <c r="G20">
-        <v>0.008398856049752473</v>
+        <v>0.004756157938627185</v>
       </c>
       <c r="H20">
         <v>132</v>
       </c>
       <c r="I20">
-        <v>-1.264529505582137</v>
+        <v>-0.2971301359459254</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -1133,25 +1133,25 @@
         <v>28</v>
       </c>
       <c r="C21">
-        <v>-0.01367947975420856</v>
+        <v>-0.002959497981595211</v>
       </c>
       <c r="D21">
-        <v>0.8123190552137922</v>
+        <v>0.3477865117338803</v>
       </c>
       <c r="E21">
-        <v>-0.126165011912703</v>
+        <v>-0.0432470010514735</v>
       </c>
       <c r="F21">
-        <v>0.1494418698395061</v>
+        <v>0.6224543809522978</v>
       </c>
       <c r="G21">
-        <v>0.00943354014332011</v>
+        <v>0.005996307053307792</v>
       </c>
       <c r="H21">
         <v>132</v>
       </c>
       <c r="I21">
-        <v>-0.9796927925875296</v>
+        <v>-0.03990772385509239</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -1162,25 +1162,25 @@
         <v>29</v>
       </c>
       <c r="C22">
-        <v>-0.01287667468462968</v>
+        <v>-0.00196929259303707</v>
       </c>
       <c r="D22">
-        <v>0.8924625958836483</v>
+        <v>0.4198093719146351</v>
       </c>
       <c r="E22">
-        <v>-0.114433583088871</v>
+        <v>-0.02568831863902079</v>
       </c>
       <c r="F22">
-        <v>0.1913712291385143</v>
+        <v>0.769998036988385</v>
       </c>
       <c r="G22">
-        <v>0.009804291515940264</v>
+        <v>0.006721397051596428</v>
       </c>
       <c r="H22">
         <v>132</v>
       </c>
       <c r="I22">
-        <v>-0.7943817878028403</v>
+        <v>0.1618320422267789</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -1191,83 +1191,83 @@
         <v>30</v>
       </c>
       <c r="C23">
-        <v>-0.01187609029513409</v>
+        <v>-0.0006861837104906589</v>
       </c>
       <c r="D23">
-        <v>1.334979873927242</v>
+        <v>0.850083921926027</v>
       </c>
       <c r="E23">
-        <v>-0.1110657891395612</v>
+        <v>-0.009699857180603051</v>
       </c>
       <c r="F23">
-        <v>0.2048556323625222</v>
+        <v>0.9121036449751738</v>
       </c>
       <c r="G23">
-        <v>0.009320220905794371</v>
+        <v>0.006204159527372199</v>
       </c>
       <c r="H23">
         <v>132</v>
       </c>
       <c r="I23">
-        <v>-0.2207879547353233</v>
+        <v>0.7601938558517507</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="B24" t="s">
         <v>31</v>
       </c>
       <c r="C24">
-        <v>-0.01115954355006183</v>
+        <v>-0.0002481089955979459</v>
       </c>
       <c r="D24">
-        <v>1.206859193438141</v>
+        <v>-0.09368572947520329</v>
       </c>
       <c r="E24">
-        <v>-0.09772085324428717</v>
+        <v>-0.003461107474958947</v>
       </c>
       <c r="F24">
-        <v>0.2649708804810821</v>
+        <v>0.9685818453469869</v>
       </c>
       <c r="G24">
-        <v>0.009967905733720243</v>
+        <v>0.006287140241728497</v>
       </c>
       <c r="H24">
         <v>132</v>
       </c>
       <c r="I24">
-        <v>-0.2550410116199591</v>
+        <v>-0.1261880078985342</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="B25" t="s">
         <v>32</v>
       </c>
       <c r="C25">
-        <v>-0.01087410580580528</v>
+        <v>4.730772107230738E-06</v>
       </c>
       <c r="D25">
-        <v>0.366774132300448</v>
+        <v>0.7230739728108149</v>
       </c>
       <c r="E25">
-        <v>-0.09809820729272492</v>
+        <v>5.827374982314613E-05</v>
       </c>
       <c r="F25">
-        <v>0.2631212233710434</v>
+        <v>0.9994708857014587</v>
       </c>
       <c r="G25">
-        <v>0.009675223892116112</v>
+        <v>0.007120121186139588</v>
       </c>
       <c r="H25">
         <v>132</v>
       </c>
       <c r="I25">
-        <v>-1.057733728260044</v>
+        <v>0.7236937039568621</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -1278,25 +1278,25 @@
         <v>33</v>
       </c>
       <c r="C26">
-        <v>-0.01057220601816825</v>
+        <v>0.0001215738861379679</v>
       </c>
       <c r="D26">
-        <v>0.2447269689374951</v>
+        <v>-0.2186701602491076</v>
       </c>
       <c r="E26">
-        <v>-0.09305658270802122</v>
+        <v>0.001581688268963315</v>
       </c>
       <c r="F26">
-        <v>0.2885650738077679</v>
+        <v>0.9856393439781379</v>
       </c>
       <c r="G26">
-        <v>0.009921064197522346</v>
+        <v>0.006741354822628256</v>
       </c>
       <c r="H26">
         <v>132</v>
       </c>
       <c r="I26">
-        <v>-1.140232019442546</v>
+        <v>-0.2027439811650338</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -1307,25 +1307,25 @@
         <v>34</v>
       </c>
       <c r="C27">
-        <v>-0.01050254887739822</v>
+        <v>0.0005164759574160959</v>
       </c>
       <c r="D27">
-        <v>0.6389523050049366</v>
+        <v>0.1614612288296498</v>
       </c>
       <c r="E27">
-        <v>-0.1111079567903332</v>
+        <v>0.01056910197873295</v>
       </c>
       <c r="F27">
-        <v>0.20468268039904</v>
+        <v>0.9042628148248553</v>
       </c>
       <c r="G27">
-        <v>0.008239114002632152</v>
+        <v>0.004285643947777809</v>
       </c>
       <c r="H27">
         <v>132</v>
       </c>
       <c r="I27">
-        <v>-0.7368815979342296</v>
+        <v>0.2291195792511583</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -1336,25 +1336,25 @@
         <v>35</v>
       </c>
       <c r="C28">
-        <v>-0.008633606918058501</v>
+        <v>0.002218523407756031</v>
       </c>
       <c r="D28">
-        <v>0.6014103440419228</v>
+        <v>0.1311513632566265</v>
       </c>
       <c r="E28">
-        <v>-0.07922547184720101</v>
+        <v>0.03138864626028399</v>
       </c>
       <c r="F28">
-        <v>0.3665288776596969</v>
+        <v>0.7208776024729294</v>
       </c>
       <c r="G28">
-        <v>0.009527709409717132</v>
+        <v>0.006195918611676941</v>
       </c>
       <c r="H28">
         <v>132</v>
       </c>
       <c r="I28">
-        <v>-0.5295921622237408</v>
+        <v>0.4217779296726665</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -1365,25 +1365,25 @@
         <v>36</v>
       </c>
       <c r="C29">
-        <v>-0.008609092126569027</v>
+        <v>0.002468032503187184</v>
       </c>
       <c r="D29">
-        <v>0.4132137161084531</v>
+        <v>-0.06679501784764943</v>
       </c>
       <c r="E29">
-        <v>-0.09155345366258191</v>
+        <v>0.04997856420258445</v>
       </c>
       <c r="F29">
-        <v>0.2964580450478347</v>
+        <v>0.5692852982729177</v>
       </c>
       <c r="G29">
-        <v>0.008212646702638878</v>
+        <v>0.0043256596160666</v>
       </c>
       <c r="H29">
         <v>132</v>
       </c>
       <c r="I29">
-        <v>-0.7145773524720894</v>
+        <v>0.2565172400698716</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -1394,25 +1394,25 @@
         <v>37</v>
       </c>
       <c r="C30">
-        <v>-0.006828086872281329</v>
+        <v>0.003991575921065674</v>
       </c>
       <c r="D30">
-        <v>0.5589063568010937</v>
+        <v>0.09005430242272355</v>
       </c>
       <c r="E30">
-        <v>-0.06244807091648128</v>
+        <v>0.05649200590955195</v>
       </c>
       <c r="F30">
-        <v>0.4768708575531766</v>
+        <v>0.519974556163104</v>
       </c>
       <c r="G30">
-        <v>0.009571055986333487</v>
+        <v>0.006187163914540167</v>
       </c>
       <c r="H30">
         <v>132</v>
       </c>
       <c r="I30">
-        <v>-0.3355730234677604</v>
+        <v>0.6129507480823269</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -1423,25 +1423,25 @@
         <v>38</v>
       </c>
       <c r="C31">
-        <v>-0.006594826761560389</v>
+        <v>0.004274391739237055</v>
       </c>
       <c r="D31">
-        <v>0.5786530720741246</v>
+        <v>0.1076536037062355</v>
       </c>
       <c r="E31">
-        <v>-0.05964547561245233</v>
+        <v>0.05849917702772631</v>
       </c>
       <c r="F31">
-        <v>0.4969086795356665</v>
+        <v>0.505230374053077</v>
       </c>
       <c r="G31">
-        <v>0.009680110453125093</v>
+        <v>0.006397473617881969</v>
       </c>
       <c r="H31">
         <v>132</v>
       </c>
       <c r="I31">
-        <v>-0.2852692336902863</v>
+        <v>0.6675989215462896</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -1452,25 +1452,25 @@
         <v>39</v>
       </c>
       <c r="C32">
-        <v>-0.006296440267914754</v>
+        <v>0.004479362876309441</v>
       </c>
       <c r="D32">
-        <v>0.1308259284575073</v>
+        <v>-0.3361255411255412</v>
       </c>
       <c r="E32">
-        <v>-0.05635723434182606</v>
+        <v>0.06001046839238564</v>
       </c>
       <c r="F32">
-        <v>0.5209723530609345</v>
+        <v>0.4942742068739249</v>
       </c>
       <c r="G32">
-        <v>0.00978324550125702</v>
+        <v>0.006534827670707374</v>
       </c>
       <c r="H32">
         <v>132</v>
       </c>
       <c r="I32">
-        <v>-0.6940077466393255</v>
+        <v>0.2506709956709957</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -1481,25 +1481,25 @@
         <v>40</v>
       </c>
       <c r="C33">
-        <v>-0.005284602902119976</v>
+        <v>0.005851191128410894</v>
       </c>
       <c r="D33">
-        <v>0.2007879547353231</v>
+        <v>-0.2817631199210145</v>
       </c>
       <c r="E33">
-        <v>-0.05665944660199716</v>
+        <v>0.1193014021369335</v>
       </c>
       <c r="F33">
-        <v>0.5187362479634727</v>
+        <v>0.1730390620080483</v>
       </c>
       <c r="G33">
-        <v>0.008167142378774948</v>
+        <v>0.004270849196720666</v>
       </c>
       <c r="H33">
         <v>132</v>
       </c>
       <c r="I33">
-        <v>-0.4914950254423938</v>
+        <v>0.4847429179008126</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -1510,25 +1510,25 @@
         <v>41</v>
       </c>
       <c r="C34">
-        <v>-0.004926699121154723</v>
+        <v>0.005941949773809957</v>
       </c>
       <c r="D34">
-        <v>-0.1323012075643655</v>
+        <v>-0.603275993012835</v>
       </c>
       <c r="E34">
-        <v>-0.04397648034132051</v>
+        <v>0.07759971780129687</v>
       </c>
       <c r="F34">
-        <v>0.6165906652984592</v>
+        <v>0.3764761706875716</v>
       </c>
       <c r="G34">
-        <v>0.009816203249694235</v>
+        <v>0.00669553996246089</v>
       </c>
       <c r="H34">
         <v>132</v>
       </c>
       <c r="I34">
-        <v>-0.7776987924356342</v>
+        <v>0.1751194273562694</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -1539,25 +1539,25 @@
         <v>42</v>
       </c>
       <c r="C35">
-        <v>-0.004068203124048844</v>
+        <v>0.00706189484815439</v>
       </c>
       <c r="D35">
-        <v>0.4898006379585327</v>
+        <v>0.007496392496392557</v>
       </c>
       <c r="E35">
-        <v>-0.03918754294533208</v>
+        <v>0.1071053694689566</v>
       </c>
       <c r="F35">
-        <v>0.6555107224077463</v>
+        <v>0.2215705334347679</v>
       </c>
       <c r="G35">
-        <v>0.009098068394422568</v>
+        <v>0.005749537501188468</v>
       </c>
       <c r="H35">
         <v>132</v>
       </c>
       <c r="I35">
-        <v>-0.0431339712918658</v>
+        <v>0.9326046176046177</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -1568,25 +1568,25 @@
         <v>43</v>
       </c>
       <c r="C36">
-        <v>-0.002966950686918545</v>
+        <v>0.008126692511987809</v>
       </c>
       <c r="D36">
-        <v>-0.1173061441482494</v>
+        <v>-0.5980306827675248</v>
       </c>
       <c r="E36">
-        <v>-0.03074025988486126</v>
+        <v>0.1484319612377858</v>
       </c>
       <c r="F36">
-        <v>0.7264120542100554</v>
+        <v>0.08940289591671144</v>
       </c>
       <c r="G36">
-        <v>0.008461080438517623</v>
+        <v>0.004748725189792357</v>
       </c>
       <c r="H36">
         <v>132</v>
       </c>
       <c r="I36">
-        <v>-0.5059766841345789</v>
+        <v>0.4665660363028783</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -1597,25 +1597,25 @@
         <v>44</v>
       </c>
       <c r="C37">
-        <v>-0.00294691447564087</v>
+        <v>0.008215081423197131</v>
       </c>
       <c r="D37">
-        <v>0.5076946153261943</v>
+        <v>0.02400812637654737</v>
       </c>
       <c r="E37">
-        <v>-0.02809305680631405</v>
+        <v>0.121078344609844</v>
       </c>
       <c r="F37">
-        <v>0.7491518704807886</v>
+        <v>0.166681149717978</v>
       </c>
       <c r="G37">
-        <v>0.009196560113991408</v>
+        <v>0.00590699748270208</v>
       </c>
       <c r="H37">
         <v>132</v>
       </c>
       <c r="I37">
-        <v>0.1216488190172403</v>
+        <v>1.100183792815371</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -1626,25 +1626,25 @@
         <v>45</v>
       </c>
       <c r="C38">
-        <v>-0.002851142429286262</v>
+        <v>0.008288638842073955</v>
       </c>
       <c r="D38">
-        <v>0.05897205134047243</v>
+        <v>-0.4237518037518037</v>
       </c>
       <c r="E38">
-        <v>-0.03096541320688597</v>
+        <v>0.1772901724078028</v>
       </c>
       <c r="F38">
-        <v>0.7244885888321929</v>
+        <v>0.04198434259858783</v>
       </c>
       <c r="G38">
-        <v>0.008071644839952213</v>
+        <v>0.004035450087593209</v>
       </c>
       <c r="H38">
         <v>132</v>
       </c>
       <c r="I38">
-        <v>-0.3145276068960279</v>
+        <v>0.6620598845598845</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -1655,25 +1655,25 @@
         <v>46</v>
       </c>
       <c r="C39">
-        <v>-0.002153197010569448</v>
+        <v>0.009038418391572269</v>
       </c>
       <c r="D39">
-        <v>0.1977515759094706</v>
+        <v>-0.2872184248500039</v>
       </c>
       <c r="E39">
-        <v>-0.02259394731379443</v>
+        <v>0.1699922768235346</v>
       </c>
       <c r="F39">
-        <v>0.7970640964337743</v>
+        <v>0.05133196143461466</v>
       </c>
       <c r="G39">
-        <v>0.00835620529743869</v>
+        <v>0.004595408661082761</v>
       </c>
       <c r="H39">
         <v>132</v>
       </c>
       <c r="I39">
-        <v>-0.08431723247512707</v>
+        <v>0.8968143844459635</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -1684,25 +1684,25 @@
         <v>47</v>
       </c>
       <c r="C40">
-        <v>0.001037552242855583</v>
+        <v>0.0122479646374785</v>
       </c>
       <c r="D40">
-        <v>0.1631514392040704</v>
+        <v>-0.3226330978962558</v>
       </c>
       <c r="E40">
-        <v>0.01028862491811455</v>
+        <v>0.1963411570940313</v>
       </c>
       <c r="F40">
-        <v>0.906791824942129</v>
+        <v>0.02404922362121757</v>
       </c>
       <c r="G40">
-        <v>0.008844188188090357</v>
+        <v>0.00536468575207912</v>
       </c>
       <c r="H40">
         <v>132</v>
       </c>
       <c r="I40">
-        <v>0.2990707830181517</v>
+        <v>1.281850269613428</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -1713,83 +1713,83 @@
         <v>48</v>
       </c>
       <c r="C41">
-        <v>0.001384507417050609</v>
+        <v>0.01267922147492256</v>
       </c>
       <c r="D41">
-        <v>-0.1369226095541886</v>
+        <v>-0.6263602187286396</v>
       </c>
       <c r="E41">
-        <v>0.01468070963807188</v>
+        <v>0.236405469274125</v>
       </c>
       <c r="F41">
-        <v>0.8673123989627762</v>
+        <v>0.006351623494273688</v>
       </c>
       <c r="G41">
-        <v>0.008270461725503534</v>
+        <v>0.004570621469663306</v>
       </c>
       <c r="H41">
         <v>132</v>
       </c>
       <c r="I41">
-        <v>0.04444786207944121</v>
+        <v>1.034617794486215</v>
       </c>
     </row>
     <row r="42" spans="1:9">
       <c r="A42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B42" t="s">
         <v>49</v>
       </c>
       <c r="C42">
-        <v>0.001430562874918037</v>
+        <v>0.01270251009202395</v>
       </c>
       <c r="D42">
-        <v>0.07430318219791907</v>
+        <v>-0.6455118857750436</v>
       </c>
       <c r="E42">
-        <v>0.01492319343911611</v>
+        <v>0.2215901525413291</v>
       </c>
       <c r="F42">
-        <v>0.8651413545556252</v>
+        <v>0.01066494879792629</v>
       </c>
       <c r="G42">
-        <v>0.008406692096321463</v>
+        <v>0.004902688926321363</v>
       </c>
       <c r="H42">
         <v>132</v>
       </c>
       <c r="I42">
-        <v>0.2617069188121819</v>
+        <v>1.018516936280094</v>
       </c>
     </row>
     <row r="43" spans="1:9">
       <c r="A43">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B43" t="s">
         <v>50</v>
       </c>
       <c r="C43">
-        <v>0.001455642924104156</v>
+        <v>0.01281014820187178</v>
       </c>
       <c r="D43">
-        <v>-0.1581476418318525</v>
+        <v>-0.4188121819700766</v>
       </c>
       <c r="E43">
-        <v>0.01501991369395063</v>
+        <v>0.2240936356765098</v>
       </c>
       <c r="F43">
-        <v>0.8642756630945414</v>
+        <v>0.009791963968423785</v>
       </c>
       <c r="G43">
-        <v>0.008498978817353163</v>
+        <v>0.004886129042010566</v>
       </c>
       <c r="H43">
         <v>132</v>
       </c>
       <c r="I43">
-        <v>0.03254158122579193</v>
+        <v>1.259317232475127</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -1800,25 +1800,25 @@
         <v>51</v>
       </c>
       <c r="C44">
-        <v>0.001921763117022257</v>
+        <v>0.01315325092745744</v>
       </c>
       <c r="D44">
-        <v>0.04056390977443614</v>
+        <v>-0.4461338953444217</v>
       </c>
       <c r="E44">
-        <v>0.0191233388026769</v>
+        <v>0.2110597857937614</v>
       </c>
       <c r="F44">
-        <v>0.8277091309594644</v>
+        <v>0.01512968437593786</v>
       </c>
       <c r="G44">
-        <v>0.008812213950588928</v>
+        <v>0.005342699827518608</v>
       </c>
       <c r="H44">
         <v>132</v>
       </c>
       <c r="I44">
-        <v>0.2923148781043519</v>
+        <v>1.276941976152502</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -1829,112 +1829,112 @@
         <v>52</v>
       </c>
       <c r="C45">
-        <v>0.00196434876225957</v>
+        <v>0.01335532620586859</v>
       </c>
       <c r="D45">
-        <v>0.1308806106174527</v>
+        <v>-0.3627284119389383</v>
       </c>
       <c r="E45">
-        <v>0.02006847456823961</v>
+        <v>0.2210466250763647</v>
       </c>
       <c r="F45">
-        <v>0.819335891069599</v>
+        <v>0.01086327777131957</v>
       </c>
       <c r="G45">
-        <v>0.008583118068236929</v>
+        <v>0.005167979603616522</v>
       </c>
       <c r="H45">
         <v>132</v>
       </c>
       <c r="I45">
-        <v>0.3882102984734564</v>
+        <v>1.386819321029848</v>
       </c>
     </row>
     <row r="46" spans="1:9">
       <c r="A46">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="B46" t="s">
         <v>53</v>
       </c>
       <c r="C46">
-        <v>0.00249411697181886</v>
+        <v>0.01376863828551253</v>
       </c>
       <c r="D46">
-        <v>-0.1374808232702968</v>
+        <v>-0.4178180299232927</v>
       </c>
       <c r="E46">
-        <v>0.02782030399491411</v>
+        <v>0.2110971068705724</v>
       </c>
       <c r="F46">
-        <v>0.7515075345951464</v>
+        <v>0.0151113519088926</v>
       </c>
       <c r="G46">
-        <v>0.007859865961632004</v>
+        <v>0.005591628259235299</v>
       </c>
       <c r="H46">
         <v>132</v>
       </c>
       <c r="I46">
-        <v>0.1892485000379738</v>
+        <v>1.385873585478848</v>
       </c>
     </row>
     <row r="47" spans="1:9">
       <c r="A47">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B47" t="s">
         <v>54</v>
       </c>
       <c r="C47">
-        <v>0.002500126095947712</v>
+        <v>0.01395206875620696</v>
       </c>
       <c r="D47">
-        <v>0.0704841649578492</v>
+        <v>-0.5058680792891319</v>
       </c>
       <c r="E47">
-        <v>0.02449216862982284</v>
+        <v>0.2282389195168864</v>
       </c>
       <c r="F47">
-        <v>0.7804297643586061</v>
+        <v>0.008484339617483775</v>
       </c>
       <c r="G47">
-        <v>0.008950199127191827</v>
+        <v>0.005219874880385017</v>
       </c>
       <c r="H47">
         <v>132</v>
       </c>
       <c r="I47">
-        <v>0.3980006835269995</v>
+        <v>1.32185292777398</v>
       </c>
     </row>
     <row r="48" spans="1:9">
       <c r="A48">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B48" t="s">
         <v>55</v>
       </c>
       <c r="C48">
-        <v>0.002681278143311087</v>
+        <v>0.01413401216434563</v>
       </c>
       <c r="D48">
-        <v>-0.01746715273031055</v>
+        <v>-0.6418762816131235</v>
       </c>
       <c r="E48">
-        <v>0.02698610153812701</v>
+        <v>0.2716884196890798</v>
       </c>
       <c r="F48">
-        <v>0.7587263608606799</v>
+        <v>0.001625633864087247</v>
       </c>
       <c r="G48">
-        <v>0.008711076881736727</v>
+        <v>0.004391082764347844</v>
       </c>
       <c r="H48">
         <v>132</v>
       </c>
       <c r="I48">
-        <v>0.3337802840434418</v>
+        <v>1.209679311916154</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -1945,25 +1945,25 @@
         <v>56</v>
       </c>
       <c r="C49">
-        <v>0.003696063545400631</v>
+        <v>0.01512805260896864</v>
       </c>
       <c r="D49">
-        <v>0.02828662565504658</v>
+        <v>-0.4670995670995672</v>
       </c>
       <c r="E49">
-        <v>0.03657209311020083</v>
+        <v>0.2290422032613769</v>
       </c>
       <c r="F49">
-        <v>0.6771727466291382</v>
+        <v>0.008249603283369872</v>
       </c>
       <c r="G49">
-        <v>0.00885782923737352</v>
+        <v>0.00563890188056662</v>
       </c>
       <c r="H49">
         <v>132</v>
       </c>
       <c r="I49">
-        <v>0.5124709501025292</v>
+        <v>1.514675324675325</v>
       </c>
     </row>
   </sheetData>
